--- a/data/trans_dic/IP26C_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP26C_R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año</t>
+          <t>Menores según que han tenido una quemadura en el último año (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,32; 20,15</t>
+          <t>8,42; 20,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,24; 18,67</t>
+          <t>7,02; 18,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,01; 15,72</t>
+          <t>4,29; 16,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,69; 14,75</t>
+          <t>2,95; 15,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 12,54</t>
+          <t>3,65; 12,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,13; 23,85</t>
+          <t>10,92; 24,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 14,2</t>
+          <t>3,05; 14,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,63; 23,42</t>
+          <t>7,03; 23,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,91; 14,25</t>
+          <t>6,96; 14,41</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,47; 18,85</t>
+          <t>10,04; 19,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,51; 12,64</t>
+          <t>4,72; 12,56</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,74; 17,3</t>
+          <t>6,82; 17,0</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,3; 14,22</t>
+          <t>9,05; 14,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,84; 13,76</t>
+          <t>8,97; 13,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,38; 11,76</t>
+          <t>7,41; 11,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,07; 11,89</t>
+          <t>6,96; 11,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,69; 12,12</t>
+          <t>7,81; 12,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,12; 12,47</t>
+          <t>8,22; 12,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,69; 12,17</t>
+          <t>7,62; 12,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,9; 12,9</t>
+          <t>7,75; 12,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,94; 12,39</t>
+          <t>9,06; 12,23</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,13; 12,23</t>
+          <t>8,98; 12,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,15; 11,28</t>
+          <t>8,1; 11,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,03; 11,6</t>
+          <t>8,23; 11,65</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,51; 15,32</t>
+          <t>7,42; 15,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,14; 10,93</t>
+          <t>4,13; 11,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,09; 13,66</t>
+          <t>6,03; 14,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,34; 12,59</t>
+          <t>5,09; 12,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 14,61</t>
+          <t>6,57; 15,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,92; 14,06</t>
+          <t>6,59; 13,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,23; 12,91</t>
+          <t>5,81; 12,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,93; 16,35</t>
+          <t>8,06; 16,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,03; 13,62</t>
+          <t>8,11; 13,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,62; 11,47</t>
+          <t>6,15; 11,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,96; 12,07</t>
+          <t>7,0; 12,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,61; 13,12</t>
+          <t>7,84; 13,2</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,7; 13,84</t>
+          <t>9,61; 13,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,56; 12,34</t>
+          <t>8,8; 12,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,59; 11,28</t>
+          <t>7,62; 11,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 10,91</t>
+          <t>7,25; 11,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 11,24</t>
+          <t>7,78; 11,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,17; 12,9</t>
+          <t>9,25; 12,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,64; 11,15</t>
+          <t>7,65; 11,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,86; 12,95</t>
+          <t>8,86; 12,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,28; 11,91</t>
+          <t>9,14; 11,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,38; 12,08</t>
+          <t>9,31; 11,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,16; 10,68</t>
+          <t>8,15; 10,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,69; 11,49</t>
+          <t>8,66; 11,58</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores según que han tenido una quemadura en el último año (tasa de respuesta: 99,31%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>12247</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10999</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5100</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4131</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5796</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>14506</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5060</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>8787</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>18043</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>25505</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>10160</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>12918</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>7653; 18406</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6488; 17054</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2526; 9549</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1613; 8402</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3147; 11149</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>9416; 21000</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2091; 9732</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>4357; 14658</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>12315; 25508</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>17930; 34063</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6012; 16009</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>7953; 19839</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>47643</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>50366</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>44280</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>43204</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>46087</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>49577</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>46705</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>52384</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>93731</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>99943</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>90984</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>95589</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>37602; 58750</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>40157; 62472</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>34667; 55878</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>31930; 54584</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>36944; 57337</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>40092; 61614</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>36848; 58577</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>39990; 65171</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>80472; 108610</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>84008; 115840</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>77038; 108027</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>80212; 113569</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>19017</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11854</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16160</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12384</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>15716</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>17200</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>16887</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>21625</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>34734</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>29054</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>33047</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>34009</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>12806; 26299</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6740; 18086</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10278; 24022</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7617; 18300</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>10302; 23818</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>11221; 23811</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10810; 24014</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>14783; 30330</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>26713; 44299</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>20523; 38450</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>24985; 43246</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>26088; 43955</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>78908</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>73218</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>65539</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>59719</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>67600</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81283</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>68652</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>82796</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>146507</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>154501</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>134191</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>142515</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>65248; 92607</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>61927; 87534</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>53124; 78190</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>48026; 73821</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>55686; 81987</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>68855; 96516</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>56504; 83849</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>67496; 98738</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>127529; 165580</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>134732; 173651</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>116934; 152569</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>123293; 164986</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP26C_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP26C_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año (tasa de respuesta: 99,31%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,42; 20,26</t>
+          <t>8,29; 20,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,02; 18,46</t>
+          <t>6,9; 18,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 16,24</t>
+          <t>4,29; 16,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 15,37</t>
+          <t>3,02; 15,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,65; 12,94</t>
+          <t>3,56; 13,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,92; 24,36</t>
+          <t>11,04; 24,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 14,18</t>
+          <t>3,14; 14,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,03; 23,64</t>
+          <t>7,17; 23,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 14,41</t>
+          <t>6,86; 14,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,04; 19,08</t>
+          <t>10,74; 19,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,72; 12,56</t>
+          <t>4,53; 12,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,82; 17,0</t>
+          <t>6,6; 17,28</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,05; 14,14</t>
+          <t>9,26; 14,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,97; 13,95</t>
+          <t>8,88; 14,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,41; 11,95</t>
+          <t>7,38; 12,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,96; 11,9</t>
+          <t>7,07; 12,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,81; 12,13</t>
+          <t>7,61; 12,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,22; 12,63</t>
+          <t>8,18; 12,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 12,11</t>
+          <t>7,54; 12,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,75; 12,63</t>
+          <t>7,82; 12,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,06; 12,23</t>
+          <t>8,72; 12,2</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,98; 12,38</t>
+          <t>8,94; 12,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,1; 11,36</t>
+          <t>8,15; 11,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,23; 11,65</t>
+          <t>8,06; 11,48</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,42; 15,23</t>
+          <t>7,51; 15,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,13; 11,07</t>
+          <t>4,4; 11,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,03; 14,09</t>
+          <t>6,22; 13,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,09; 12,24</t>
+          <t>5,08; 12,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,57; 15,19</t>
+          <t>6,7; 14,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,59; 13,98</t>
+          <t>6,59; 14,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 12,9</t>
+          <t>6,03; 12,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,06; 16,54</t>
+          <t>8,32; 16,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,11; 13,44</t>
+          <t>8,04; 13,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,15; 11,52</t>
+          <t>6,37; 11,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,0; 12,12</t>
+          <t>7,03; 12,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,84; 13,2</t>
+          <t>7,74; 13,52</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,61; 13,64</t>
+          <t>9,67; 13,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,8; 12,44</t>
+          <t>8,77; 12,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,62; 11,22</t>
+          <t>7,7; 11,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 11,14</t>
+          <t>7,16; 11,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,78; 11,45</t>
+          <t>7,8; 11,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,25; 12,97</t>
+          <t>9,09; 12,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,65; 11,35</t>
+          <t>7,51; 11,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,86; 12,97</t>
+          <t>8,8; 13,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,14; 11,87</t>
+          <t>9,28; 11,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,31; 11,99</t>
+          <t>9,43; 12,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,15; 10,63</t>
+          <t>8,16; 10,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,66; 11,58</t>
+          <t>8,56; 11,56</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año (tasa de respuesta: 99,31%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7653; 18406</t>
+          <t>7534; 18314</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6488; 17054</t>
+          <t>6370; 16888</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2526; 9549</t>
+          <t>2520; 9807</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1613; 8402</t>
+          <t>1653; 8378</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3147; 11149</t>
+          <t>3066; 11234</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9416; 21000</t>
+          <t>9513; 20988</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2091; 9732</t>
+          <t>2153; 10074</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4357; 14658</t>
+          <t>4445; 14783</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12315; 25508</t>
+          <t>12134; 24955</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17930; 34063</t>
+          <t>19186; 34129</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6012; 16009</t>
+          <t>5770; 16026</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7953; 19839</t>
+          <t>7705; 20166</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37602; 58750</t>
+          <t>38472; 58790</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40157; 62472</t>
+          <t>39794; 62688</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34667; 55878</t>
+          <t>34525; 56119</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31930; 54584</t>
+          <t>32414; 55298</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36944; 57337</t>
+          <t>35975; 57310</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40092; 61614</t>
+          <t>39899; 60769</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36848; 58577</t>
+          <t>36497; 58516</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39990; 65171</t>
+          <t>40371; 65409</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>80472; 108610</t>
+          <t>77478; 108334</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84008; 115840</t>
+          <t>83656; 115005</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77038; 108027</t>
+          <t>77492; 107147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>80212; 113569</t>
+          <t>78515; 111874</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12806; 26299</t>
+          <t>12978; 26452</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6740; 18086</t>
+          <t>7189; 18637</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10278; 24022</t>
+          <t>10613; 23563</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7617; 18300</t>
+          <t>7591; 18347</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10302; 23818</t>
+          <t>10508; 22388</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11221; 23811</t>
+          <t>11228; 24583</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10810; 24014</t>
+          <t>11230; 23994</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14783; 30330</t>
+          <t>15253; 30420</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26713; 44299</t>
+          <t>26479; 44834</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20523; 38450</t>
+          <t>21245; 38164</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24985; 43246</t>
+          <t>25062; 43432</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26088; 43955</t>
+          <t>25765; 45022</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65248; 92607</t>
+          <t>65682; 92845</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>61927; 87534</t>
+          <t>61693; 87705</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53124; 78190</t>
+          <t>53642; 78767</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48026; 73821</t>
+          <t>47477; 73561</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55686; 81987</t>
+          <t>55832; 80371</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68855; 96516</t>
+          <t>67687; 95718</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>56504; 83849</t>
+          <t>55483; 82556</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>67496; 98738</t>
+          <t>67044; 99187</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>127529; 165580</t>
+          <t>129479; 165012</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>134732; 173651</t>
+          <t>136554; 175619</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>116934; 152569</t>
+          <t>117201; 152216</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>123293; 164986</t>
+          <t>121956; 164653</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP26C_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP26C_R-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,73%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16,83%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15,65%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>13,48%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11,91%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8,67%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,56%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,73%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16,83%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,29; 20,15</t>
+          <t>3,09; 12,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,9; 18,28</t>
+          <t>11,13; 23,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 16,67</t>
+          <t>3,12; 14,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 15,32</t>
+          <t>8,41; 25,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 13,04</t>
+          <t>8,32; 20,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,04; 24,35</t>
+          <t>7,24; 18,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,14; 14,68</t>
+          <t>4,01; 15,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,17; 23,84</t>
+          <t>3,77; 17,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 14,1</t>
+          <t>6,91; 14,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,74; 19,11</t>
+          <t>10,47; 18,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,53; 12,58</t>
+          <t>4,51; 12,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,6; 17,28</t>
+          <t>7,84; 19,5</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10,16%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9,65%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10,49%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>11,47%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>11,25%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>9,47%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9,42%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,75%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>10,16%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,65%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,26; 14,15</t>
+          <t>7,69; 12,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,88; 14,0</t>
+          <t>8,12; 12,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,38; 12,0</t>
+          <t>7,69; 12,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,07; 12,06</t>
+          <t>8,22; 13,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,61; 12,12</t>
+          <t>9,3; 14,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,18; 12,46</t>
+          <t>8,84; 13,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,54; 12,1</t>
+          <t>7,38; 11,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,82; 12,67</t>
+          <t>7,87; 12,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,72; 12,2</t>
+          <t>8,94; 12,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,94; 12,29</t>
+          <t>9,13; 12,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,15; 11,26</t>
+          <t>8,15; 11,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,06; 11,48</t>
+          <t>8,53; 12,12</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10,1%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,07%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>11,01%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7,26%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>9,48%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,28%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,02%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,07%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>6,56; 14,61</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6,92; 14,06</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6,23; 12,91</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>7,97; 16,81</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>7,51; 15,32</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>4,4; 11,41</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>6,22; 13,82</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>5,08; 12,27</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>6,7; 14,28</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,59; 14,43</t>
+          <t>4,14; 10,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,03; 12,89</t>
+          <t>6,09; 13,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,32; 16,59</t>
+          <t>5,57; 12,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,04; 13,61</t>
+          <t>8,03; 13,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,37; 11,44</t>
+          <t>6,62; 11,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,03; 12,18</t>
+          <t>6,96; 12,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,74; 13,52</t>
+          <t>7,75; 13,39</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9,44%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10,92%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11,29%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>11,62%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10,41%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>9,4%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,01%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,44%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,92%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,67; 13,67</t>
+          <t>7,86; 11,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,77; 12,47</t>
+          <t>9,17; 12,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,7; 11,3</t>
+          <t>7,64; 11,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,16; 11,1</t>
+          <t>9,13; 13,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,8; 11,23</t>
+          <t>9,7; 13,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,09; 12,86</t>
+          <t>8,56; 12,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,51; 11,18</t>
+          <t>7,59; 11,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,8; 13,02</t>
+          <t>7,78; 11,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,28; 11,83</t>
+          <t>9,28; 11,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,43; 12,13</t>
+          <t>9,38; 12,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,16; 10,6</t>
+          <t>8,16; 10,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,56; 11,56</t>
+          <t>9,22; 12,11</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5796</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14506</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5060</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8879</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>12247</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>10999</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>5100</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4131</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5796</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>14506</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5060</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8787</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12918</t>
+          <t>13215</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7534; 18314</t>
+          <t>2666; 10804</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6370; 16888</t>
+          <t>9592; 20556</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2520; 9807</t>
+          <t>2144; 9744</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1653; 8378</t>
+          <t>4770; 14486</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3066; 11234</t>
+          <t>7558; 18309</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9513; 20988</t>
+          <t>6691; 17248</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2153; 10074</t>
+          <t>2361; 9248</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4445; 14783</t>
+          <t>1764; 8257</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12134; 24955</t>
+          <t>12231; 25226</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19186; 34129</t>
+          <t>18690; 33662</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5770; 16026</t>
+          <t>5744; 16112</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7705; 20166</t>
+          <t>8118; 20185</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>66</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>46087</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>49577</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>46705</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>49869</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>47643</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>50366</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>44280</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>43204</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>46087</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>49577</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>46705</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>52384</t>
+          <t>43496</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95589</t>
+          <t>93365</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38472; 58790</t>
+          <t>36372; 57302</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39794; 62688</t>
+          <t>39621; 60839</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34525; 56119</t>
+          <t>37217; 58891</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32414; 55298</t>
+          <t>39088; 63105</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35975; 57310</t>
+          <t>38659; 59087</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39899; 60769</t>
+          <t>39594; 61626</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36497; 58516</t>
+          <t>34526; 54973</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40371; 65409</t>
+          <t>33861; 54866</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77478; 108334</t>
+          <t>79401; 110090</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>83656; 115005</t>
+          <t>85401; 114392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77492; 107147</t>
+          <t>77576; 107274</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>78515; 111874</t>
+          <t>77272; 109768</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>15716</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17200</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16887</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>20368</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>19017</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>11854</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>16160</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>12384</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>15716</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>17200</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>16887</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21625</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34009</t>
+          <t>33312</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12978; 26452</t>
+          <t>10279; 22904</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7189; 18637</t>
+          <t>11784; 23944</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10613; 23563</t>
+          <t>11597; 24030</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7591; 18347</t>
+          <t>13426; 28317</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10508; 22388</t>
+          <t>12964; 26463</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11228; 24583</t>
+          <t>6753; 17844</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11230; 23994</t>
+          <t>10378; 23296</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15253; 30420</t>
+          <t>8352; 19271</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26479; 44834</t>
+          <t>26451; 44871</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21245; 38164</t>
+          <t>22082; 38266</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25062; 43432</t>
+          <t>24828; 43037</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25765; 45022</t>
+          <t>24676; 42644</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>95</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>67600</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>81283</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>68652</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>79116</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>78908</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>73218</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>65539</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>59719</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>67600</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81283</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>68652</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>82796</t>
+          <t>60776</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>142515</t>
+          <t>139892</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65682; 92845</t>
+          <t>56272; 80488</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>61693; 87705</t>
+          <t>68247; 96003</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53642; 78767</t>
+          <t>56425; 82320</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47477; 73561</t>
+          <t>63956; 94496</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55832; 80371</t>
+          <t>65895; 93971</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67687; 95718</t>
+          <t>60202; 86826</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>55483; 82556</t>
+          <t>52926; 78613</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>67044; 99187</t>
+          <t>48759; 73877</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>129479; 165012</t>
+          <t>129378; 166082</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>136554; 175619</t>
+          <t>135745; 174869</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>117201; 152216</t>
+          <t>117083; 153372</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>121956; 164653</t>
+          <t>122446; 160807</t>
         </is>
       </c>
     </row>
